--- a/template/header_template_aizu.xlsx
+++ b/template/header_template_aizu.xlsx
@@ -1281,14 +1281,46 @@
           <t>南大橋</t>
         </is>
       </c>
-      <c r="AW1" s="3" t="n"/>
-      <c r="AX1" s="3" t="n"/>
-      <c r="AY1" s="3" t="n"/>
-      <c r="AZ1" s="3" t="n"/>
-      <c r="BA1" s="3" t="n"/>
-      <c r="BB1" s="3" t="n"/>
-      <c r="BC1" s="3" t="n"/>
-      <c r="BD1" s="3" t="n"/>
+      <c r="AW1" s="3" t="inlineStr">
+        <is>
+          <t>湯川橋</t>
+        </is>
+      </c>
+      <c r="AX1" s="3" t="inlineStr">
+        <is>
+          <t>鶴沼橋</t>
+        </is>
+      </c>
+      <c r="AY1" s="3" t="inlineStr">
+        <is>
+          <t>馬越</t>
+        </is>
+      </c>
+      <c r="AZ1" s="3" t="inlineStr">
+        <is>
+          <t>小豆沢</t>
+        </is>
+      </c>
+      <c r="BA1" s="3" t="inlineStr">
+        <is>
+          <t>一の戸川</t>
+        </is>
+      </c>
+      <c r="BB1" s="3" t="inlineStr">
+        <is>
+          <t>宮川</t>
+        </is>
+      </c>
+      <c r="BC1" s="3" t="inlineStr">
+        <is>
+          <t>大谷川</t>
+        </is>
+      </c>
+      <c r="BD1" s="3" t="inlineStr">
+        <is>
+          <t>大橋</t>
+        </is>
+      </c>
       <c r="BE1" s="3" t="n"/>
       <c r="BF1" s="3" t="n"/>
       <c r="BG1" s="2" t="n"/>

--- a/template/header_template_aizu.xlsx
+++ b/template/header_template_aizu.xlsx
@@ -1278,7 +1278,7 @@
       </c>
       <c r="AV1" s="3" t="inlineStr">
         <is>
-          <t>南大橋</t>
+          <t>身神川排水機場</t>
         </is>
       </c>
       <c r="AW1" s="3" t="inlineStr">
@@ -1321,9 +1321,21 @@
           <t>大橋</t>
         </is>
       </c>
-      <c r="BE1" s="3" t="n"/>
-      <c r="BF1" s="3" t="n"/>
-      <c r="BG1" s="2" t="n"/>
+      <c r="BE1" s="3" t="inlineStr">
+        <is>
+          <t>高田</t>
+        </is>
+      </c>
+      <c r="BF1" s="3" t="inlineStr">
+        <is>
+          <t>宮古</t>
+        </is>
+      </c>
+      <c r="BG1" s="2" t="inlineStr">
+        <is>
+          <t>福島</t>
+        </is>
+      </c>
       <c r="BH1" s="3" t="n"/>
       <c r="BI1" s="3" t="n"/>
     </row>

--- a/template/header_template_aizu.xlsx
+++ b/template/header_template_aizu.xlsx
@@ -1336,7 +1336,11 @@
           <t>福島</t>
         </is>
       </c>
-      <c r="BH1" s="3" t="n"/>
+      <c r="BH1" s="3" t="inlineStr">
+        <is>
+          <t>大石</t>
+        </is>
+      </c>
       <c r="BI1" s="3" t="n"/>
     </row>
     <row r="2">
